--- a/education_forms/037_homework_help_order_form--education_forms.xlsx
+++ b/education_forms/037_homework_help_order_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'call_me',_'value':_'call_me'}</t>
+          <t>call_me</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Call Me', 'value': 'call_me'}</t>
+          <t>Call Me</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'chat_with_me',_'value':_'chat_with_me'}</t>
+          <t>chat_with_me</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Chat With Me', 'value': 'chat_with_me'}</t>
+          <t>Chat With Me</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'meet_in_person',_'value':_'meet_in_person'}</t>
+          <t>meet_in_person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Meet In Person', 'value': 'meet_in_person'}</t>
+          <t>Meet In Person</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'student',_'value':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Student', 'value': 'student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'teacher',_'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher', 'value': 'teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree',_'value':_'i_agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I Agree', 'value': 'i_agree'}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_agree',_'value':_'i_do_not_agree'}</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'I Do Not Agree', 'value': 'i_do_not_agree'}</t>
+          <t>I Do Not Agree</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'i_agree',_'value':_'agree'}</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'I Agree', 'value': 'agree'}</t>
+          <t>I Agree</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_agree',_'value':_'disagree'}</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'I Do Not Agree', 'value': 'disagree'}</t>
+          <t>I Do Not Agree</t>
         </is>
       </c>
     </row>
